--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -793,7 +793,7 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="1">
-    <x:tablePart r:id="rId1"/>
+    <x:tablePart r:id="rId8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -63,7 +63,7 @@
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -84,6 +84,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF00008B"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -696,11 +696,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.270624999999999" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.980625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.580625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.280625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -154,7 +154,7 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thick">
@@ -171,7 +171,7 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thick">
+      <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
       <x:top style="thick">
@@ -707,10 +707,10 @@
       <x:c r="B2" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s"/>
-      <x:c r="D2" s="2" t="s"/>
-      <x:c r="E2" s="2" t="s"/>
-      <x:c r="F2" s="3" t="s"/>
+      <x:c r="C2" s="3" t="s"/>
+      <x:c r="D2" s="3" t="s"/>
+      <x:c r="E2" s="3" t="s"/>
+      <x:c r="F2" s="2" t="s"/>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="B3" s="4" t="s">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -271,115 +271,115 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="18">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="7" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="14">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -61,7 +61,7 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
+    <x:numFmt numFmtId="165" formatCode="$ #,##0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -298,7 +298,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -310,7 +310,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -363,7 +363,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -379,7 +379,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
